--- a/images/images2.xlsx
+++ b/images/images2.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df63a93e45125bfa/Documents/zenn-contents/public/images/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{5958D91A-36D7-452C-BC5F-CB571CDA66A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EC87D87-0C3A-4C37-9FF6-58663B47576D}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{5958D91A-36D7-452C-BC5F-CB571CDA66A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5231C05-15BA-4E5E-85B2-9AA1B4C76540}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="11295" xr2:uid="{B2770CEC-1F6F-4BB2-A9B4-F5DDD5D60A2C}"/>
+    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{B2770CEC-1F6F-4BB2-A9B4-F5DDD5D60A2C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet5" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1461,6 +1462,99 @@
         </xdr:spPr>
       </xdr:pic>
     </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>171000</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>11863</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFA374D7-3D27-84D9-4B13-4451C02440F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="238125"/>
+          <a:ext cx="3600000" cy="2154988"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>171000</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>11864</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32F0B007-B2EA-4E49-8BCE-F5B1ACDCC130}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="681606" y="2595344"/>
+          <a:ext cx="3579027" cy="2135327"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1774,4 +1868,15 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2DC9CFD-607E-4F85-80FE-9D7617725CC2}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>